--- a/sources/gunjack_step5b.xlsx
+++ b/sources/gunjack_step5b.xlsx
@@ -1165,6 +1165,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
@@ -1207,6 +1212,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
@@ -1259,6 +1269,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
@@ -1306,6 +1321,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
@@ -1353,6 +1373,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
@@ -1393,6 +1418,11 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>251f1e2f-c3c7-4333-a3d4-49d19c52d36c</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -6573,6 +6603,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
+        </is>
+      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
@@ -6605,6 +6640,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
+        </is>
+      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
@@ -6637,6 +6677,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
@@ -6667,6 +6712,11 @@
       <c r="K119" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>2fc42861-9255-4a82-8966-00993ca4d00e</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">

--- a/sources/gunjack_step5b.xlsx
+++ b/sources/gunjack_step5b.xlsx
@@ -3269,7 +3269,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3522,7 +3522,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Df+1+2</t>
+          <t>DF,1+2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4799,7 +4799,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5806,6 +5806,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -5923,6 +5928,11 @@
       <c r="A101" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
